--- a/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,1</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>0,0; 9,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A07-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -840,24 +840,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,6</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
     </row>
@@ -1172,22 +1172,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1488,24 +1488,24 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
